--- a/docs/FatherFlow-content-werkboek.xlsx
+++ b/docs/FatherFlow-content-werkboek.xlsx
@@ -14,6 +14,9 @@
     <sheet name="Herhaling" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="Themamodel" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="Nieuwe oefeningen" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Jaarritme" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Raamwerken" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Oefenpool" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -121,7 +124,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -159,6 +162,12 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -770,6 +779,365 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D23"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="62" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Oefenpool — acht per thema, gemengd getrokken</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Hoe de acht oefeningen van een thema over de sessies verdeeld worden.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="32" customHeight="1">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>Regel</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>Wat het betekent</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>Waarom</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="16" t="inlineStr">
+        <is>
+          <t>Pool van 8</t>
+        </is>
+      </c>
+      <c r="B5" s="13" t="inlineStr">
+        <is>
+          <t>Elk thema heeft acht oefeningen. Een sessie trekt er drie.</t>
+        </is>
+      </c>
+      <c r="C5" s="13" t="inlineStr">
+        <is>
+          <t>Acht is genoeg om twaalf sessies te vullen zonder dat het uitgekauwd raakt, en klein genoeg om per band te schrijven.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="16" t="inlineStr">
+        <is>
+          <t>Gewogen, niet willekeurig</t>
+        </is>
+      </c>
+      <c r="B6" s="13" t="inlineStr">
+        <is>
+          <t>Volgorde van voorrang: nog nooit gezien &gt; eerder fout of onzeker &gt; lang geleden &gt; recent goed.</t>
+        </is>
+      </c>
+      <c r="C6" s="13" t="inlineStr">
+        <is>
+          <t>Zuiver willekeurig geeft dubbelingen in dezelfde sessie en laat zwakke plekken liggen. Dit is Duolingo's kern.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="16" t="inlineStr">
+        <is>
+          <t>Nooit twee keer hetzelfde type</t>
+        </is>
+      </c>
+      <c r="B7" s="13" t="inlineStr">
+        <is>
+          <t>Binnen één sessie komt elk vraagtype hoogstens één keer voor.</t>
+        </is>
+      </c>
+      <c r="C7" s="13" t="inlineStr">
+        <is>
+          <t>Afwisseling is het hele punt. Drie keer 'beste aanpak' achter elkaar is precies wat er nu misgaat.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="16" t="inlineStr">
+        <is>
+          <t>Minstens één niet-scoorbare</t>
+        </is>
+      </c>
+      <c r="B8" s="13" t="inlineStr">
+        <is>
+          <t>Elke sessie bevat een Terugblik of een Jouw eerste neiging.</t>
+        </is>
+      </c>
+      <c r="C8" s="13" t="inlineStr">
+        <is>
+          <t>Anders voelt het als een toets. Een van de drie moet een vraag zijn waar geen goed antwoord op bestaat.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="16" t="inlineStr">
+        <is>
+          <t>Hooguit één 'beste aanpak'</t>
+        </is>
+      </c>
+      <c r="B9" s="13" t="inlineStr">
+        <is>
+          <t>Van de acht in een pool zijn er maximaal twee van dit type, en per sessie hooguit één.</t>
+        </is>
+      </c>
+      <c r="C9" s="13" t="inlineStr">
+        <is>
+          <t>Dit is het gokbare type. Het mag bestaan, maar het mag het thema niet dragen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="16" t="inlineStr">
+        <is>
+          <t>Fouten voorrang</t>
+        </is>
+      </c>
+      <c r="B10" s="13" t="inlineStr">
+        <is>
+          <t>Een fout beantwoorde oefening komt terug in de eerstvolgende sessie.</t>
+        </is>
+      </c>
+      <c r="C10" s="13" t="inlineStr">
+        <is>
+          <t>Fouten die niet terugkomen leren niets.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="16" t="inlineStr">
+        <is>
+          <t>Skelet en situatie apart</t>
+        </is>
+      </c>
+      <c r="B11" s="13" t="inlineStr">
+        <is>
+          <t>Een oefening is een skelet (de vorm plus het punt) en een situatie (de scène). Hetzelfde skelet krijgt per band en geslacht een andere scène.</t>
+        </is>
+      </c>
+      <c r="C11" s="13" t="inlineStr">
+        <is>
+          <t>Zo schrijf je 48 skeletten en ongeveer 120 situaties in plaats van 864 losse oefeningen. Dit is wat het jaarlijkse vernieuwen betaalbaar maakt.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>VOORBEELDVERDELING VAN ÉÉN POOL</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="32" customHeight="1">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>Vraagtype</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>Rol in het thema</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>Skelet gedeeld over banden?</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="34" customHeight="1">
+      <c r="A16" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="B16" s="13" t="inlineStr">
+        <is>
+          <t>Waar ging het mis</t>
+        </is>
+      </c>
+      <c r="C16" s="13" t="inlineStr">
+        <is>
+          <t>Opent het thema. Herkennen is makkelijker dan bedenken.</t>
+        </is>
+      </c>
+      <c r="D16" s="17" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="34" customHeight="1">
+      <c r="A17" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="B17" s="13" t="inlineStr">
+        <is>
+          <t>Jouw eerste neiging</t>
+        </is>
+      </c>
+      <c r="C17" s="13" t="inlineStr">
+        <is>
+          <t>Peilt waar deze vader staat. Geen goed antwoord.</t>
+        </is>
+      </c>
+      <c r="D17" s="17" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="34" customHeight="1">
+      <c r="A18" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B18" s="13" t="inlineStr">
+        <is>
+          <t>Twee redelijke wegen</t>
+        </is>
+      </c>
+      <c r="C18" s="13" t="inlineStr">
+        <is>
+          <t>Kern van het thema. Het hangt ervan af, en waarvan precies.</t>
+        </is>
+      </c>
+      <c r="D18" s="17" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="34" customHeight="1">
+      <c r="A19" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="B19" s="13" t="inlineStr">
+        <is>
+          <t>Twee redelijke wegen</t>
+        </is>
+      </c>
+      <c r="C19" s="13" t="inlineStr">
+        <is>
+          <t>Zelfde vorm, andere situatie, ander afhankelijkheidspunt.</t>
+        </is>
+      </c>
+      <c r="D19" s="17" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="34" customHeight="1">
+      <c r="A20" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="B20" s="13" t="inlineStr">
+        <is>
+          <t>Eén woord verschil</t>
+        </is>
+      </c>
+      <c r="C20" s="13" t="inlineStr">
+        <is>
+          <t>Precisie in taal. Hier zit de meeste winst thuis.</t>
+        </is>
+      </c>
+      <c r="D20" s="13" t="inlineStr">
+        <is>
+          <t>Deels</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="34" customHeight="1">
+      <c r="A21" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="B21" s="13" t="inlineStr">
+        <is>
+          <t>En dan?</t>
+        </is>
+      </c>
+      <c r="C21" s="13" t="inlineStr">
+        <is>
+          <t>Toetst het mentale model van dit kind op deze leeftijd.</t>
+        </is>
+      </c>
+      <c r="D21" s="15" t="inlineStr">
+        <is>
+          <t>Nee</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="34" customHeight="1">
+      <c r="A22" s="13" t="n">
+        <v>7</v>
+      </c>
+      <c r="B22" s="13" t="inlineStr">
+        <is>
+          <t>Zet op volgorde</t>
+        </is>
+      </c>
+      <c r="C22" s="13" t="inlineStr">
+        <is>
+          <t>Volgorde als vaardigheid. Niet te gokken op toon.</t>
+        </is>
+      </c>
+      <c r="D22" s="17" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="34" customHeight="1">
+      <c r="A23" s="13" t="n">
+        <v>8</v>
+      </c>
+      <c r="B23" s="13" t="inlineStr">
+        <is>
+          <t>Beste aanpak</t>
+        </is>
+      </c>
+      <c r="C23" s="13" t="inlineStr">
+        <is>
+          <t>Het enige gokbare type in de pool. Alleen waar er echt één betere reactie is.</t>
+        </is>
+      </c>
+      <c r="D23" s="17" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -4744,4 +5112,849 @@
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="80" customWidth="1" min="3" max="3"/>
+    <col width="66" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Jaarritme — de verjaardag is het nieuwjaar</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Geel = knoppen om aan te draaien. De contentkosten onderaan rekenen mee.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="32" customHeight="1">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>Moment</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>Wanneer</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>Wat er gebeurt</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>Waarom dit moment</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="76" customHeight="1">
+      <c r="A5" s="16" t="inlineStr">
+        <is>
+          <t>Verjaardag</t>
+        </is>
+      </c>
+      <c r="B5" s="13" t="inlineStr">
+        <is>
+          <t>Elk jaar, op de dag zelf</t>
+        </is>
+      </c>
+      <c r="C5" s="13" t="inlineStr">
+        <is>
+          <t>Een kort 'nieuw jaar'-scherm: wat verandert er bij een kind van deze leeftijd, wat vroeg je vorig jaar het vaakst, wat komt eraan. Daarna wordt het pad opnieuw gevuld.</t>
+        </is>
+      </c>
+      <c r="D5" s="13" t="inlineStr">
+        <is>
+          <t>De enige datum in het jaar die écht over het kind gaat. Geen app-datum, geen abonnementsdatum. Een vader voelt zelf al dat er iets verschuift; de app sluit daarop aan in plaats van een eigen ritme op te leggen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="76" customHeight="1">
+      <c r="A6" s="16" t="inlineStr">
+        <is>
+          <t>Bandgrens</t>
+        </is>
+      </c>
+      <c r="B6" s="13" t="inlineStr">
+        <is>
+          <t>3× in de 8 jaar dat hij de app gebruikt</t>
+        </is>
+      </c>
+      <c r="C6" s="13" t="inlineStr">
+        <is>
+          <t>Een echte nieuwe set thema's. Dochter bij 10, 13 en 15; zoon bij 11, 14 en 16.</t>
+        </is>
+      </c>
+      <c r="D6" s="13" t="inlineStr">
+        <is>
+          <t>Alleen hier verandert de ontwikkelingsfase werkelijk. Elk jaar zes nieuwe thema's beloven is niet vol te houden en ook niet waar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="76" customHeight="1">
+      <c r="A7" s="16" t="inlineStr">
+        <is>
+          <t>Jaar binnen dezelfde band</t>
+        </is>
+      </c>
+      <c r="B7" s="13" t="inlineStr">
+        <is>
+          <t>De andere jaren</t>
+        </is>
+      </c>
+      <c r="C7" s="13" t="inlineStr">
+        <is>
+          <t>Dezelfde thema's, maar scherpere situaties en een nieuwe trekking uit de oefenpool. Wat hij vorig jaar afmaakte staat als onderhoud, niet opnieuw als nieuw.</t>
+        </is>
+      </c>
+      <c r="D7" s="13" t="inlineStr">
+        <is>
+          <t>Een band duurt 1 tot 3 jaar. Het verschil tussen 11 en 12 is echt, maar zit in de situatie, niet in het thema.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="76" customHeight="1">
+      <c r="A8" s="16" t="inlineStr">
+        <is>
+          <t>Thema</t>
+        </is>
+      </c>
+      <c r="B8" s="13" t="inlineStr">
+        <is>
+          <t>Elke 6 weken</t>
+        </is>
+      </c>
+      <c r="C8" s="13" t="inlineStr">
+        <is>
+          <t>4 weken nieuw materiaal, 2 weken consolidatie en checkpoint. Zes thema's vullen zo 36 weken.</t>
+        </is>
+      </c>
+      <c r="D8" s="13" t="inlineStr">
+        <is>
+          <t>Een maand is te kort voor acht oefeningen plus een gewoonte die moet beklijven. Zes weken × zes thema's landt precies op een verjaardag-tot-verjaardag cyclus, met lucht.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="76" customHeight="1">
+      <c r="A9" s="16" t="inlineStr">
+        <is>
+          <t>Sessie</t>
+        </is>
+      </c>
+      <c r="B9" s="13" t="inlineStr">
+        <is>
+          <t>2× per week, 5-7 minuten</t>
+        </is>
+      </c>
+      <c r="C9" s="13" t="inlineStr">
+        <is>
+          <t>3 of 4 oefeningen, getrokken uit de pool van 8. Zie tabblad Oefenpool.</t>
+        </is>
+      </c>
+      <c r="D9" s="13" t="inlineStr">
+        <is>
+          <t>Kort genoeg om vol te houden op een doordeweekse avond. Vaker aanbieden dan dit levert geen extra gedragsverandering op, alleen schuldgevoel.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="76" customHeight="1">
+      <c r="A10" s="16" t="inlineStr">
+        <is>
+          <t>Lucht</t>
+        </is>
+      </c>
+      <c r="B10" s="13" t="inlineStr">
+        <is>
+          <t>Ongeveer 12 weken per jaar</t>
+        </is>
+      </c>
+      <c r="C10" s="13" t="inlineStr">
+        <is>
+          <t>Geen nieuw thema. Alleen onderhoud, opfrissers en de chat.</t>
+        </is>
+      </c>
+      <c r="D10" s="13" t="inlineStr">
+        <is>
+          <t>Vakanties, drukke periodes, en het simpele feit dat 52 weken nieuw materiaal niemand volhoudt. Ingebouwde rust is eerlijker dan een pad dat stilstaat en aanvoelt als falen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>KNOPPEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="32" customHeight="1">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>Instelling</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>Waarde</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>Toelichting</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="26" customHeight="1">
+      <c r="A14" s="13" t="inlineStr">
+        <is>
+          <t>Thema's per jaar</t>
+        </is>
+      </c>
+      <c r="B14" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="C14" s="13" t="inlineStr">
+        <is>
+          <t>Zes × zes weken = 36 weken actief.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="26" customHeight="1">
+      <c r="A15" s="13" t="inlineStr">
+        <is>
+          <t>Weken per thema</t>
+        </is>
+      </c>
+      <c r="B15" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="C15" s="13" t="inlineStr">
+        <is>
+          <t>Vier weken nieuw, twee weken consolidatie.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="26" customHeight="1">
+      <c r="A16" s="13" t="inlineStr">
+        <is>
+          <t>Oefeningen per thema</t>
+        </is>
+      </c>
+      <c r="B16" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="C16" s="13" t="inlineStr">
+        <is>
+          <t>De pool waaruit elke sessie trekt.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="26" customHeight="1">
+      <c r="A17" s="13" t="inlineStr">
+        <is>
+          <t>Oefeningen per sessie</t>
+        </is>
+      </c>
+      <c r="B17" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="C17" s="13" t="inlineStr">
+        <is>
+          <t>Uit de pool van acht. Nooit twee keer hetzelfde type achter elkaar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="26" customHeight="1">
+      <c r="A18" s="13" t="inlineStr">
+        <is>
+          <t>Sessies per week</t>
+        </is>
+      </c>
+      <c r="B18" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="C18" s="13" t="inlineStr">
+        <is>
+          <t>Wat telt als contact voor de streak.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="26" customHeight="1">
+      <c r="A19" s="13" t="inlineStr">
+        <is>
+          <t>Lessen per thema</t>
+        </is>
+      </c>
+      <c r="B19" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="C19" s="13" t="inlineStr">
+        <is>
+          <t>Naast de oefeningen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>WAT DAT KOST</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="32" customHeight="1">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>Berekening</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>Uitkomst</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="inlineStr">
+        <is>
+          <t>Toelichting</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="42" customHeight="1">
+      <c r="A23" s="13" t="inlineStr">
+        <is>
+          <t>Actieve weken per jaar</t>
+        </is>
+      </c>
+      <c r="B23" s="19">
+        <f>B14*B15</f>
+        <v/>
+      </c>
+      <c r="C23" s="13" t="inlineStr">
+        <is>
+          <t>Thema's per jaar × weken per thema.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="42" customHeight="1">
+      <c r="A24" s="13" t="inlineStr">
+        <is>
+          <t>Oefeningen per jaar per profiel</t>
+        </is>
+      </c>
+      <c r="B24" s="19">
+        <f>B14*B16</f>
+        <v/>
+      </c>
+      <c r="C24" s="13" t="inlineStr">
+        <is>
+          <t>Wat één vader in één jaar te zien krijgt.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="42" customHeight="1">
+      <c r="A25" s="13" t="inlineStr">
+        <is>
+          <t>Sessies per thema</t>
+        </is>
+      </c>
+      <c r="B25" s="19">
+        <f>B15*B18</f>
+        <v/>
+      </c>
+      <c r="C25" s="13" t="inlineStr">
+        <is>
+          <t>Weken per thema × sessies per week.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="42" customHeight="1">
+      <c r="A26" s="13" t="inlineStr">
+        <is>
+          <t>Oefening-vertoningen per thema</t>
+        </is>
+      </c>
+      <c r="B26" s="19">
+        <f>B15*B18*B17</f>
+        <v/>
+      </c>
+      <c r="C26" s="13" t="inlineStr">
+        <is>
+          <t>Meer dan acht, dus elke oefening komt meerdere keren terug. Precies de bedoeling: dat is de herhaling.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="42" customHeight="1">
+      <c r="A27" s="13" t="inlineStr">
+        <is>
+          <t>Als elk jaar volledig nieuw zou zijn</t>
+        </is>
+      </c>
+      <c r="B27" s="15">
+        <f>864</f>
+        <v/>
+      </c>
+      <c r="C27" s="13" t="inlineStr">
+        <is>
+          <t>6 thema's × 8 oefeningen × alle jaren in alle acht band-geslacht-combinaties. Onhaalbaar, en daarom niet het model.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="42" customHeight="1">
+      <c r="A28" s="17" t="inlineStr">
+        <is>
+          <t>Skeletten (mechaniek + principe)</t>
+        </is>
+      </c>
+      <c r="B28" s="17">
+        <f>B14*B16</f>
+        <v/>
+      </c>
+      <c r="C28" s="17" t="inlineStr">
+        <is>
+          <t>Eén skelet is de oefenvorm plus het onderliggende punt. Die zijn niet leeftijdsgebonden en worden gedeeld over alle banden.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="42" customHeight="1">
+      <c r="A29" s="17" t="inlineStr">
+        <is>
+          <t>Situaties om te schrijven</t>
+        </is>
+      </c>
+      <c r="B29" s="17">
+        <f>B14*B16*2.5</f>
+        <v/>
+      </c>
+      <c r="C29" s="17" t="inlineStr">
+        <is>
+          <t>Gemiddeld tweeënhalve situatievariant per skelet. Dít is het echte schrijfwerk, en het is af te maken.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="46" customHeight="1">
+      <c r="A31" s="20" t="inlineStr">
+        <is>
+          <t>De twee groene regels zijn de kern: je schrijft niet 864 oefeningen, je schrijft 48 skeletten en ongeveer 120 situaties. Een skelet is de vorm en het punt ("twee redelijke wegen, en het hangt af van wat eraan voorafging"); de situatie is de scène, en die verschilt wél per leeftijd en geslacht.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D23"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="74" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Drie raamwerken voor de opbouw van een thema</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Drie manieren om een thema in te richten. Kies er één, of combineer per thema in de laatste kolom.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="32" customHeight="1">
+      <c r="A4" s="7" t="inlineStr"/>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>A — De boog</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>B — De gereedschapskist</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>C — De lus</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="66" customHeight="1">
+      <c r="A5" s="16" t="inlineStr">
+        <is>
+          <t>In één zin</t>
+        </is>
+      </c>
+      <c r="B5" s="13" t="inlineStr">
+        <is>
+          <t>Het thema is één verhaal in vier lessen: herkennen, begrijpen, proberen, volhouden.</t>
+        </is>
+      </c>
+      <c r="C5" s="13" t="inlineStr">
+        <is>
+          <t>Het thema is een kist met vier tot zes losse situaties. De vader pakt wat past bij zijn week.</t>
+        </is>
+      </c>
+      <c r="D5" s="13" t="inlineStr">
+        <is>
+          <t>Het thema begint met een peiling, en bedient de vader daarna op maat: oefeningen eerst, uitleg alleen waar het hapert.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="66" customHeight="1">
+      <c r="A6" s="16" t="inlineStr">
+        <is>
+          <t>Volgorde</t>
+        </is>
+      </c>
+      <c r="B6" s="13" t="inlineStr">
+        <is>
+          <t>Vast. Les 2 heeft les 1 nodig.</t>
+        </is>
+      </c>
+      <c r="C6" s="13" t="inlineStr">
+        <is>
+          <t>Vrij. Elke situatie staat op zichzelf.</t>
+        </is>
+      </c>
+      <c r="D6" s="13" t="inlineStr">
+        <is>
+          <t>Door het systeem bepaald, op basis van wat hij fout of onzeker doet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="66" customHeight="1">
+      <c r="A7" s="16" t="inlineStr">
+        <is>
+          <t>Sessie ziet eruit als</t>
+        </is>
+      </c>
+      <c r="B7" s="13" t="inlineStr">
+        <is>
+          <t>Eén les plus twee oefeningen uit die les, en één opfrisser uit de vorige.</t>
+        </is>
+      </c>
+      <c r="C7" s="13" t="inlineStr">
+        <is>
+          <t>Eén situatie plus drie oefeningen uit de hele themapool.</t>
+        </is>
+      </c>
+      <c r="D7" s="13" t="inlineStr">
+        <is>
+          <t>Vier oefeningen uit de pool. Struikelt hij, dan schuift de bijbehorende micro-les ertussen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="66" customHeight="1">
+      <c r="A8" s="16" t="inlineStr">
+        <is>
+          <t>Oefenmix</t>
+        </is>
+      </c>
+      <c r="B8" s="13" t="inlineStr">
+        <is>
+          <t>Loopt mee met de boog: herkennen vroeg (Waar ging het mis), produceren laat (Eén woord verschil).</t>
+        </is>
+      </c>
+      <c r="C8" s="13" t="inlineStr">
+        <is>
+          <t>Willekeurig uit de pool van acht, gewogen op wat hij nog niet zag.</t>
+        </is>
+      </c>
+      <c r="D8" s="13" t="inlineStr">
+        <is>
+          <t>Adaptief. Types waarop hij zwak scoort komen vaker.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="66" customHeight="1">
+      <c r="A9" s="16" t="inlineStr">
+        <is>
+          <t>Herhaling</t>
+        </is>
+      </c>
+      <c r="B9" s="13" t="inlineStr">
+        <is>
+          <t>Checkpoint aan het eind van de boog.</t>
+        </is>
+      </c>
+      <c r="C9" s="13" t="inlineStr">
+        <is>
+          <t>Doorlopend: elke sessie mengt oude en nieuwe situaties.</t>
+        </is>
+      </c>
+      <c r="D9" s="13" t="inlineStr">
+        <is>
+          <t>Ingebouwd — de peiling is meteen de herhaling van vorig jaar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="66" customHeight="1">
+      <c r="A10" s="16" t="inlineStr">
+        <is>
+          <t>Sterk</t>
+        </is>
+      </c>
+      <c r="B10" s="13" t="inlineStr">
+        <is>
+          <t>Samenhang en emotionele opbouw. Voelt als een verhaal met een einde, en dat einde is een echt moment.</t>
+        </is>
+      </c>
+      <c r="C10" s="13" t="inlineStr">
+        <is>
+          <t>Sluit aan bij de week die hij nu heeft. Geen enkele les voelt als omweg. Laagste drempel om te beginnen.</t>
+        </is>
+      </c>
+      <c r="D10" s="13" t="inlineStr">
+        <is>
+          <t>Respecteert ervaring. Een vader die dit al kan wordt niet door vier lessen gesleept. Snelste weg naar waarde.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="66" customHeight="1">
+      <c r="A11" s="16" t="inlineStr">
+        <is>
+          <t>Zwak</t>
+        </is>
+      </c>
+      <c r="B11" s="13" t="inlineStr">
+        <is>
+          <t>Wie op les 2 vastloopt komt nooit bij les 4. En als zijn probleem in les 4 zit, moet hij eerst drie lessen door.</t>
+        </is>
+      </c>
+      <c r="C11" s="13" t="inlineStr">
+        <is>
+          <t>Geen opbouw. Het risico is dat alles even oppervlakkig blijft en niets zich verdiept.</t>
+        </is>
+      </c>
+      <c r="D11" s="13" t="inlineStr">
+        <is>
+          <t>Vraagt de meeste content én de meeste logica. Zonder een ruime pool valt het adaptieve stuk meteen door de mand.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="66" customHeight="1">
+      <c r="A12" s="16" t="inlineStr">
+        <is>
+          <t>Bouwlast</t>
+        </is>
+      </c>
+      <c r="B12" s="13" t="inlineStr">
+        <is>
+          <t>Laag. Dicht bij wat er nu al staat.</t>
+        </is>
+      </c>
+      <c r="C12" s="13" t="inlineStr">
+        <is>
+          <t>Midden. Situaties moeten echt los van elkaar kunnen staan.</t>
+        </is>
+      </c>
+      <c r="D12" s="13" t="inlineStr">
+        <is>
+          <t>Hoog. Peiling, scoremodel per type, en een pool die groot genoeg is om te kunnen kiezen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="66" customHeight="1">
+      <c r="A13" s="16" t="inlineStr">
+        <is>
+          <t>Past bij</t>
+        </is>
+      </c>
+      <c r="B13" s="13" t="inlineStr">
+        <is>
+          <t>Fundament-thema's waar de volgorde er echt toe doet. Bijvoorbeeld Contact maken.</t>
+        </is>
+      </c>
+      <c r="C13" s="13" t="inlineStr">
+        <is>
+          <t>Thema's waar de vader met een concreet probleem binnenkomt. Schermen, Als het escaleert.</t>
+        </is>
+      </c>
+      <c r="D13" s="13" t="inlineStr">
+        <is>
+          <t>Het tweede jaar in dezelfde band, als hij de thema's al eens deed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="32" customHeight="1">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>ADVIES</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>Niet één raamwerk voor alles kiezen. B is de standaard, A voor het fundament, C pas in jaar twee.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="32" customHeight="1">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>Thema</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>Raamwerk</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>Waarom</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>Jouw keuze</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="40" customHeight="1">
+      <c r="A18" s="16" t="inlineStr">
+        <is>
+          <t>Contact maken</t>
+        </is>
+      </c>
+      <c r="B18" s="13" t="inlineStr">
+        <is>
+          <t>A — De boog</t>
+        </is>
+      </c>
+      <c r="C18" s="13" t="inlineStr">
+        <is>
+          <t>Fundament. De volgorde doet er hier echt toe: binnenlopen zonder agenda gaat vooraf aan een gevoelig gesprek.</t>
+        </is>
+      </c>
+      <c r="D18" s="10" t="inlineStr"/>
+    </row>
+    <row r="19" ht="40" customHeight="1">
+      <c r="A19" s="16" t="inlineStr">
+        <is>
+          <t>Als het escaleert</t>
+        </is>
+      </c>
+      <c r="B19" s="13" t="inlineStr">
+        <is>
+          <t>B — Gereedschapskist</t>
+        </is>
+      </c>
+      <c r="C19" s="13" t="inlineStr">
+        <is>
+          <t>Hier komt hij binnen met een acuut probleem. Laat hem meteen bij zijn eigen situatie.</t>
+        </is>
+      </c>
+      <c r="D19" s="10" t="inlineStr"/>
+    </row>
+    <row r="20" ht="40" customHeight="1">
+      <c r="A20" s="16" t="inlineStr">
+        <is>
+          <t>Regels en ruimte</t>
+        </is>
+      </c>
+      <c r="B20" s="13" t="inlineStr">
+        <is>
+          <t>B — Gereedschapskist</t>
+        </is>
+      </c>
+      <c r="C20" s="13" t="inlineStr">
+        <is>
+          <t>Elke regelkwestie staat op zichzelf; bedtijd en telefoon delen geen opbouw.</t>
+        </is>
+      </c>
+      <c r="D20" s="10" t="inlineStr"/>
+    </row>
+    <row r="21" ht="40" customHeight="1">
+      <c r="A21" s="16" t="inlineStr">
+        <is>
+          <t>Hoe hij naar zichzelf kijkt</t>
+        </is>
+      </c>
+      <c r="B21" s="13" t="inlineStr">
+        <is>
+          <t>A — De boog</t>
+        </is>
+      </c>
+      <c r="C21" s="13" t="inlineStr">
+        <is>
+          <t>Traag thema dat juist wél opbouw nodig heeft, van herkennen naar benoemen.</t>
+        </is>
+      </c>
+      <c r="D21" s="10" t="inlineStr"/>
+    </row>
+    <row r="22" ht="40" customHeight="1">
+      <c r="A22" s="16" t="inlineStr">
+        <is>
+          <t>Vrienden en de groep</t>
+        </is>
+      </c>
+      <c r="B22" s="13" t="inlineStr">
+        <is>
+          <t>B — Gereedschapskist</t>
+        </is>
+      </c>
+      <c r="C22" s="13" t="inlineStr">
+        <is>
+          <t>Situatie-afhankelijk en sterk leeftijdsgebonden.</t>
+        </is>
+      </c>
+      <c r="D22" s="10" t="inlineStr"/>
+    </row>
+    <row r="23" ht="40" customHeight="1">
+      <c r="A23" s="16" t="inlineStr">
+        <is>
+          <t>Schermen en online</t>
+        </is>
+      </c>
+      <c r="B23" s="13" t="inlineStr">
+        <is>
+          <t>B — Gereedschapskist</t>
+        </is>
+      </c>
+      <c r="C23" s="13" t="inlineStr">
+        <is>
+          <t>Vaakst de aanleiding om de app te openen. Nul drempel.</t>
+        </is>
+      </c>
+      <c r="D23" s="10" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B15:D15"/>
+  </mergeCells>
+  <dataValidations count="1">
+    <dataValidation sqref="D18:D23" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"A — De boog,B — Gereedschapskist,C — De lus"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>